--- a/history_data/usage_history-temp.xlsx
+++ b/history_data/usage_history-temp.xlsx
@@ -428,61 +428,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>设备编号</t>
+          <t>Machine No.</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>门店名称</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>出料时间段</t>
+          <t>Usage Period</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>出料时间段天数</t>
+          <t>Usage Days</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>原料名称</t>
+          <t>Ingredient</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>rawMaterial_EN</t>
+          <t>Ingredient No.</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>原料代码</t>
+          <t>Shelf Life (months)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Shelf Life</t>
+          <t>Price ($)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Package_Size_Base</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Package_Size_Base</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>adjusted_usage</t>
         </is>
@@ -501,40 +496,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>冰糖糖浆 Fructose Syrup</t>
+          <t>Fructose Syrup</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fructose Syrup</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
           <t>M13</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>18 months</t>
-        </is>
+      <c r="G2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H2" t="n">
+        <v>15.6</v>
       </c>
       <c r="I2" t="n">
-        <v>15.6</v>
+        <v>2000</v>
       </c>
       <c r="J2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+        <v>3031</v>
       </c>
     </row>
     <row r="3">
@@ -550,40 +538,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>冰勃朗 Ice Blanc</t>
+          <t>Ice Blanc</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ice Blanc</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
           <t>M14</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>9 months</t>
-        </is>
+      <c r="G3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+        <v>18603</v>
       </c>
     </row>
     <row r="4">
@@ -599,40 +580,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>锡兰红茶茶汤 Black Tea</t>
+          <t>Black Tea</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Black Tea</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
           <t>M16</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>24 months</t>
-        </is>
+      <c r="G4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12.3</v>
       </c>
       <c r="I4" t="n">
-        <v>12.3</v>
+        <v>500</v>
       </c>
       <c r="J4" t="n">
-        <v>500</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+        <v>636.9</v>
       </c>
     </row>
     <row r="5">
@@ -648,32 +622,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>冰水 Cold Water</t>
+          <t>Cold Water</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cold Water</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
           <t>M22</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="J5" t="n">
+        <v>34753</v>
       </c>
     </row>
     <row r="6">
@@ -689,40 +658,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>茉莉雪芽茶汤 Green Tea</t>
+          <t>Green Tea</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Green Tea</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
           <t>M23</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>24 months</t>
-        </is>
+      <c r="G6" t="n">
+        <v>24</v>
+      </c>
+      <c r="H6" t="n">
+        <v>16.2</v>
       </c>
       <c r="I6" t="n">
-        <v>16.2</v>
+        <v>500</v>
       </c>
       <c r="J6" t="n">
-        <v>500</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+        <v>718.26</v>
       </c>
     </row>
     <row r="7">
@@ -738,40 +700,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>黑糖糖浆 Brown Sugar</t>
+          <t>Brown Sugar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brown Sugar</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
           <t>M27</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>18 months</t>
-        </is>
+      <c r="G7" t="n">
+        <v>18</v>
+      </c>
+      <c r="H7" t="n">
+        <v>15.6</v>
       </c>
       <c r="I7" t="n">
-        <v>15.6</v>
+        <v>2000</v>
       </c>
       <c r="J7" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="8">
@@ -787,40 +742,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>蜜桃糖浆 Peach Syrup</t>
+          <t>Peach Syrup</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Peach Syrup</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
           <t>M28</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>18 months</t>
-        </is>
+      <c r="G8" t="n">
+        <v>18</v>
+      </c>
+      <c r="H8" t="n">
+        <v>16.8</v>
       </c>
       <c r="I8" t="n">
-        <v>16.8</v>
+        <v>2000</v>
       </c>
       <c r="J8" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+        <v>15945</v>
       </c>
     </row>
     <row r="9">
@@ -836,31 +784,26 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>荔枝糖浆 Lychee Syrup</t>
+          <t>Lychee Syrup</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lychee Syrup</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
           <t>M29</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
+      <c r="J9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -877,40 +820,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>芒果糖浆 Mango Syrup</t>
+          <t>Mango Syrup</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mango Syrup</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
           <t>M30</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>18 months</t>
-        </is>
+      <c r="G10" t="n">
+        <v>18</v>
+      </c>
+      <c r="H10" t="n">
+        <v>15.6</v>
       </c>
       <c r="I10" t="n">
-        <v>15.6</v>
+        <v>2000</v>
       </c>
       <c r="J10" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+        <v>17867</v>
       </c>
     </row>
     <row r="11">
@@ -926,11 +862,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -939,18 +875,13 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Testing Material 1</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
           <t>T01</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
+      <c r="J11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -967,11 +898,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -980,18 +911,13 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Testing Material 2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
           <t>T02</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
+      <c r="J12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1008,11 +934,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1021,18 +947,13 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Testing Material 3</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
           <t>T03</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
+      <c r="J13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1049,31 +970,26 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>饮品奶油 BC01 Beverage Cream</t>
+          <t>BC01 Beverage Cream</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>BC01 Beverage Cream</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
           <t>M32</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="n">
+      <c r="J14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1090,31 +1006,26 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Taro Syrup 鲜芋糖浆</t>
+          <t>Taro Syrup</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Taro Syrup</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
           <t>T04</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
+      <c r="J15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1131,11 +1042,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1144,18 +1055,13 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Watermelon Syrup</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
           <t>M31</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
+      <c r="J16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1172,11 +1078,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1185,18 +1091,13 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange Syrup</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
           <t>M33</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
+      <c r="J17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1213,11 +1114,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1226,19 +1127,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Passion Fruit Syrup</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
           <t>M34</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="J18" t="n">
+        <v>565</v>
       </c>
     </row>
     <row r="19">
@@ -1254,31 +1150,26 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>全脂牛奶 Whole Milk</t>
+          <t>Whole Milk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Whole Milk</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
           <t>M35</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
+      <c r="J19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1295,477 +1186,413 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>石榴糖浆 Pomegranate Syrup</t>
+          <t>Pomegranate Syrup</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pomegranate Syrup</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
           <t>MT14</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
+      <c r="J20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ZW01654</t>
+          <t>ZW01622</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Thyme Japanese Cuisine</t>
+          <t>Saga Fusion</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>冰糖糖浆 Fructose Syrup</t>
+          <t>Fructose Syrup</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fructose Syrup</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
           <t>M13</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>18 months</t>
-        </is>
+      <c r="G21" t="n">
+        <v>18</v>
+      </c>
+      <c r="H21" t="n">
+        <v>15.6</v>
       </c>
       <c r="I21" t="n">
-        <v>15.6</v>
+        <v>2000</v>
       </c>
       <c r="J21" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2915</v>
+        <v>8313</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ZW01654</t>
+          <t>ZW01622</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Thyme Japanese Cuisine</t>
+          <t>Saga Fusion</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>冰勃朗 Ice Blanc</t>
+          <t>Ice Blanc</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ice Blanc</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
           <t>M14</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>9 months</t>
-        </is>
+      <c r="G22" t="n">
+        <v>9</v>
+      </c>
+      <c r="H22" t="n">
+        <v>12</v>
       </c>
       <c r="I22" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K22" t="n">
-        <v>4357</v>
+        <v>14856</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ZW01654</t>
+          <t>ZW01622</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Thyme Japanese Cuisine</t>
+          <t>Saga Fusion</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>锡兰红茶茶汤 Black Tea</t>
+          <t>Black Tea</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Black Tea</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
           <t>M16</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>24 months</t>
-        </is>
+      <c r="G23" t="n">
+        <v>24</v>
+      </c>
+      <c r="H23" t="n">
+        <v>12.3</v>
       </c>
       <c r="I23" t="n">
-        <v>12.3</v>
+        <v>500</v>
       </c>
       <c r="J23" t="n">
-        <v>500</v>
-      </c>
-      <c r="K23" t="n">
-        <v>402.9</v>
+        <v>962.34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ZW01654</t>
+          <t>ZW01622</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Thyme Japanese Cuisine</t>
+          <t>Saga Fusion</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>冰水 Cold Water</t>
+          <t>Cold Water</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cold Water</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
           <t>M22</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="n">
-        <v>18215</v>
+      <c r="J24" t="n">
+        <v>55744</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ZW01654</t>
+          <t>ZW01622</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Thyme Japanese Cuisine</t>
+          <t>Saga Fusion</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>茉莉雪芽茶汤 Green Tea</t>
+          <t>Green Tea</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Green Tea</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
           <t>M23</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>24 months</t>
-        </is>
+      <c r="G25" t="n">
+        <v>24</v>
+      </c>
+      <c r="H25" t="n">
+        <v>16.2</v>
       </c>
       <c r="I25" t="n">
-        <v>16.2</v>
+        <v>500</v>
       </c>
       <c r="J25" t="n">
-        <v>500</v>
-      </c>
-      <c r="K25" t="n">
-        <v>306</v>
+        <v>1264.65</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ZW01654</t>
+          <t>ZW01622</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Thyme Japanese Cuisine</t>
+          <t>Saga Fusion</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>黑糖糖浆 Brown Sugar</t>
+          <t>Brown Sugar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brown Sugar</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
           <t>M27</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>18 months</t>
-        </is>
+      <c r="G26" t="n">
+        <v>18</v>
+      </c>
+      <c r="H26" t="n">
+        <v>15.6</v>
       </c>
       <c r="I26" t="n">
-        <v>15.6</v>
+        <v>2000</v>
       </c>
       <c r="J26" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K26" t="n">
-        <v>4975</v>
+        <v>4308</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ZW01654</t>
+          <t>ZW01622</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Thyme Japanese Cuisine</t>
+          <t>Saga Fusion</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>蜜桃糖浆 Peach Syrup</t>
+          <t>Peach Syrup</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Peach Syrup</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
           <t>M28</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>18 months</t>
-        </is>
+      <c r="G27" t="n">
+        <v>18</v>
+      </c>
+      <c r="H27" t="n">
+        <v>16.8</v>
       </c>
       <c r="I27" t="n">
-        <v>16.8</v>
+        <v>2000</v>
       </c>
       <c r="J27" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2520</v>
+        <v>6786</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ZW01654</t>
+          <t>ZW01622</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Thyme Japanese Cuisine</t>
+          <t>Saga Fusion</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>荔枝糖浆 Lychee Syrup</t>
+          <t>Lychee Syrup</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lychee Syrup</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
           <t>M29</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="J28" t="n">
+        <v>3480</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ZW01654</t>
+          <t>ZW01622</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Thyme Japanese Cuisine</t>
+          <t>Saga Fusion</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>芒果糖浆 Mango Syrup</t>
+          <t>Mango Syrup</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mango Syrup</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
           <t>M30</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>18 months</t>
-        </is>
+      <c r="G29" t="n">
+        <v>18</v>
+      </c>
+      <c r="H29" t="n">
+        <v>15.6</v>
       </c>
       <c r="I29" t="n">
-        <v>15.6</v>
+        <v>2000</v>
       </c>
       <c r="J29" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3345</v>
+        <v>7382</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ZW01654</t>
+          <t>ZW01622</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Thyme Japanese Cuisine</t>
+          <t>Saga Fusion</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1774,39 +1601,34 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Testing Material 1</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
           <t>T01</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="J30" t="n">
+        <v>390</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ZW01654</t>
+          <t>ZW01622</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Thyme Japanese Cuisine</t>
+          <t>Saga Fusion</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1815,39 +1637,34 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Testing Material 2</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
           <t>T02</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="n">
+      <c r="J31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ZW01654</t>
+          <t>ZW01622</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Thyme Japanese Cuisine</t>
+          <t>Saga Fusion</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1856,121 +1673,106 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Testing Material 3</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
           <t>T03</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="n">
+      <c r="J32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ZW01654</t>
+          <t>ZW01622</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Thyme Japanese Cuisine</t>
+          <t>Saga Fusion</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>饮品奶油 BC01 Beverage Cream</t>
+          <t>BC01 Beverage Cream</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>BC01 Beverage Cream</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
           <t>M32</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="n">
+      <c r="J33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ZW01654</t>
+          <t>ZW01622</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Thyme Japanese Cuisine</t>
+          <t>Saga Fusion</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Taro Syrup 鲜芋糖浆</t>
+          <t>Taro Syrup</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Taro Syrup</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
           <t>T04</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="J34" t="n">
+        <v>7064</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ZW01654</t>
+          <t>ZW01622</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Thyme Japanese Cuisine</t>
+          <t>Saga Fusion</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1979,39 +1781,34 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Watermelon Syrup</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
           <t>M31</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="n">
+      <c r="J35" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ZW01654</t>
+          <t>ZW01622</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Thyme Japanese Cuisine</t>
+          <t>Saga Fusion</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2020,39 +1817,34 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange Syrup</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
           <t>M33</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="n">
+      <c r="J36" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ZW01654</t>
+          <t>ZW01622</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Thyme Japanese Cuisine</t>
+          <t>Saga Fusion</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2061,546 +1853,472 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Passion Fruit Syrup</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
           <t>M34</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="n">
+      <c r="J37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ZW01654</t>
+          <t>ZW01622</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Thyme Japanese Cuisine</t>
+          <t>Saga Fusion</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>全脂牛奶 Whole Milk</t>
+          <t>Whole Milk</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Whole Milk</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
           <t>M35</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="J38" t="n">
+        <v>5595</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ZW01654</t>
+          <t>ZW01622</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Thyme Japanese Cuisine</t>
+          <t>Saga Fusion</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>石榴糖浆 Pomegranate Syrup</t>
+          <t>Pomegranate Syrup</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pomegranate Syrup</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
           <t>MT14</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="n">
+      <c r="J39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ZW01622</t>
+          <t>ZW01654</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Saga Fusion</t>
+          <t>Thyme Japanese Cuisine</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>冰糖糖浆 Fructose Syrup</t>
+          <t>Fructose Syrup</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fructose Syrup</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
           <t>M13</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>18 months</t>
-        </is>
+      <c r="G40" t="n">
+        <v>18</v>
+      </c>
+      <c r="H40" t="n">
+        <v>15.6</v>
       </c>
       <c r="I40" t="n">
-        <v>15.6</v>
+        <v>2000</v>
       </c>
       <c r="J40" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+        <v>2928</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ZW01622</t>
+          <t>ZW01654</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Saga Fusion</t>
+          <t>Thyme Japanese Cuisine</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>冰勃朗 Ice Blanc</t>
+          <t>Ice Blanc</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ice Blanc</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
           <t>M14</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>9 months</t>
-        </is>
+      <c r="G41" t="n">
+        <v>9</v>
+      </c>
+      <c r="H41" t="n">
+        <v>12</v>
       </c>
       <c r="I41" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="J41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+        <v>15130</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ZW01622</t>
+          <t>ZW01654</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Saga Fusion</t>
+          <t>Thyme Japanese Cuisine</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>锡兰红茶茶汤 Black Tea</t>
+          <t>Black Tea</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Black Tea</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
           <t>M16</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>24 months</t>
-        </is>
+      <c r="G42" t="n">
+        <v>24</v>
+      </c>
+      <c r="H42" t="n">
+        <v>12.3</v>
       </c>
       <c r="I42" t="n">
-        <v>12.3</v>
+        <v>500</v>
       </c>
       <c r="J42" t="n">
-        <v>500</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+        <v>992.85</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ZW01622</t>
+          <t>ZW01654</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Saga Fusion</t>
+          <t>Thyme Japanese Cuisine</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>冰水 Cold Water</t>
+          <t>Cold Water</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cold Water</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
           <t>M22</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="J43" t="n">
+        <v>36585</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ZW01622</t>
+          <t>ZW01654</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Saga Fusion</t>
+          <t>Thyme Japanese Cuisine</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>茉莉雪芽茶汤 Green Tea</t>
+          <t>Green Tea</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Green Tea</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
           <t>M23</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>24 months</t>
-        </is>
+      <c r="G44" t="n">
+        <v>24</v>
+      </c>
+      <c r="H44" t="n">
+        <v>16.2</v>
       </c>
       <c r="I44" t="n">
-        <v>16.2</v>
+        <v>500</v>
       </c>
       <c r="J44" t="n">
-        <v>500</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+        <v>665.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ZW01622</t>
+          <t>ZW01654</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Saga Fusion</t>
+          <t>Thyme Japanese Cuisine</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>黑糖糖浆 Brown Sugar</t>
+          <t>Brown Sugar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brown Sugar</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
           <t>M27</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>18 months</t>
-        </is>
+      <c r="G45" t="n">
+        <v>18</v>
+      </c>
+      <c r="H45" t="n">
+        <v>15.6</v>
       </c>
       <c r="I45" t="n">
-        <v>15.6</v>
+        <v>2000</v>
       </c>
       <c r="J45" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+        <v>7295</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ZW01622</t>
+          <t>ZW01654</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Saga Fusion</t>
+          <t>Thyme Japanese Cuisine</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>蜜桃糖浆 Peach Syrup</t>
+          <t>Peach Syrup</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Peach Syrup</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
           <t>M28</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>18 months</t>
-        </is>
+      <c r="G46" t="n">
+        <v>18</v>
+      </c>
+      <c r="H46" t="n">
+        <v>16.8</v>
       </c>
       <c r="I46" t="n">
-        <v>16.8</v>
+        <v>2000</v>
       </c>
       <c r="J46" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+        <v>8450</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ZW01622</t>
+          <t>ZW01654</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Saga Fusion</t>
+          <t>Thyme Japanese Cuisine</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>荔枝糖浆 Lychee Syrup</t>
+          <t>Lychee Syrup</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lychee Syrup</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
           <t>M29</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="n">
+      <c r="J47" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ZW01622</t>
+          <t>ZW01654</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Saga Fusion</t>
+          <t>Thyme Japanese Cuisine</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>芒果糖浆 Mango Syrup</t>
+          <t>Mango Syrup</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mango Syrup</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
           <t>M30</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>18 months</t>
-        </is>
+      <c r="G48" t="n">
+        <v>18</v>
+      </c>
+      <c r="H48" t="n">
+        <v>15.6</v>
       </c>
       <c r="I48" t="n">
-        <v>15.6</v>
+        <v>2000</v>
       </c>
       <c r="J48" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+        <v>10433</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ZW01622</t>
+          <t>ZW01654</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Saga Fusion</t>
+          <t>Thyme Japanese Cuisine</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2609,39 +2327,34 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Testing Material 1</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
           <t>T01</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="n">
+      <c r="J49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ZW01622</t>
+          <t>ZW01654</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Saga Fusion</t>
+          <t>Thyme Japanese Cuisine</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2650,39 +2363,34 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Testing Material 2</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
           <t>T02</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="n">
+      <c r="J50" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ZW01622</t>
+          <t>ZW01654</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Saga Fusion</t>
+          <t>Thyme Japanese Cuisine</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2691,121 +2399,106 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Testing Material 3</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
           <t>T03</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="n">
+      <c r="J51" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ZW01622</t>
+          <t>ZW01654</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Saga Fusion</t>
+          <t>Thyme Japanese Cuisine</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>饮品奶油 BC01 Beverage Cream</t>
+          <t>BC01 Beverage Cream</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>BC01 Beverage Cream</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
           <t>M32</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="n">
+      <c r="J52" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ZW01622</t>
+          <t>ZW01654</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Saga Fusion</t>
+          <t>Thyme Japanese Cuisine</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Taro Syrup 鲜芋糖浆</t>
+          <t>Taro Syrup</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Taro Syrup</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
           <t>T04</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="n">
+      <c r="J53" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ZW01622</t>
+          <t>ZW01654</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Saga Fusion</t>
+          <t>Thyme Japanese Cuisine</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2814,39 +2507,34 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Watermelon Syrup</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
           <t>M31</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="n">
+      <c r="J54" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ZW01622</t>
+          <t>ZW01654</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Saga Fusion</t>
+          <t>Thyme Japanese Cuisine</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2855,39 +2543,34 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orange Syrup</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
           <t>M33</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="n">
+      <c r="J55" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ZW01622</t>
+          <t>ZW01654</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Saga Fusion</t>
+          <t>Thyme Japanese Cuisine</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2896,100 +2579,85 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Passion Fruit Syrup</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
           <t>M34</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="n">
+      <c r="J56" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ZW01622</t>
+          <t>ZW01654</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Saga Fusion</t>
+          <t>Thyme Japanese Cuisine</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>全脂牛奶 Whole Milk</t>
+          <t>Whole Milk</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Whole Milk</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
           <t>M35</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="n">
+      <c r="J57" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ZW01622</t>
+          <t>ZW01654</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Saga Fusion</t>
+          <t>Thyme Japanese Cuisine</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>石榴糖浆 Pomegranate Syrup</t>
+          <t>Pomegranate Syrup</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pomegranate Syrup</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
           <t>MT14</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="n">
+      <c r="J58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3004,61 +2672,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>设备编号</t>
+          <t>Machine No.</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>门店名称</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>出料时间段</t>
+          <t>Usage Period</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>出料时间段天数</t>
+          <t>Usage Days</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>原料名称</t>
+          <t>Ingredient</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>rawMaterial_EN</t>
+          <t>Ingredient No.</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>原料代码</t>
+          <t>Shelf Life (months)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Shelf Life</t>
+          <t>Price ($)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Package_Size_Base</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Package_Size_Base</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>adjusted_usage</t>
         </is>
@@ -3077,40 +2740,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>冰糖糖浆 Fructose Syrup</t>
+          <t>Fructose Syrup</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fructose Syrup</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
           <t>M13</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>18 months</t>
-        </is>
+      <c r="G2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H2" t="n">
+        <v>15.6</v>
       </c>
       <c r="I2" t="n">
-        <v>15.6</v>
+        <v>2000</v>
       </c>
       <c r="J2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+        <v>8313</v>
       </c>
     </row>
     <row r="3">
@@ -3126,40 +2782,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>冰勃朗 Ice Blanc</t>
+          <t>Ice Blanc</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ice Blanc</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
           <t>M14</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>9 months</t>
-        </is>
+      <c r="G3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+        <v>14856</v>
       </c>
     </row>
     <row r="4">
@@ -3175,40 +2824,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>锡兰红茶茶汤 Black Tea</t>
+          <t>Black Tea</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Black Tea</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
           <t>M16</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>24 months</t>
-        </is>
+      <c r="G4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12.3</v>
       </c>
       <c r="I4" t="n">
-        <v>12.3</v>
+        <v>500</v>
       </c>
       <c r="J4" t="n">
-        <v>500</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+        <v>962.34</v>
       </c>
     </row>
     <row r="5">
@@ -3224,32 +2866,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>冰水 Cold Water</t>
+          <t>Cold Water</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cold Water</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
           <t>M22</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="J5" t="n">
+        <v>55744</v>
       </c>
     </row>
     <row r="6">
@@ -3265,40 +2902,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>茉莉雪芽茶汤 Green Tea</t>
+          <t>Green Tea</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Green Tea</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
           <t>M23</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>24 months</t>
-        </is>
+      <c r="G6" t="n">
+        <v>24</v>
+      </c>
+      <c r="H6" t="n">
+        <v>16.2</v>
       </c>
       <c r="I6" t="n">
-        <v>16.2</v>
+        <v>500</v>
       </c>
       <c r="J6" t="n">
-        <v>500</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+        <v>1264.65</v>
       </c>
     </row>
     <row r="7">
@@ -3314,40 +2944,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>黑糖糖浆 Brown Sugar</t>
+          <t>Brown Sugar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brown Sugar</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
           <t>M27</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>18 months</t>
-        </is>
+      <c r="G7" t="n">
+        <v>18</v>
+      </c>
+      <c r="H7" t="n">
+        <v>15.6</v>
       </c>
       <c r="I7" t="n">
-        <v>15.6</v>
+        <v>2000</v>
       </c>
       <c r="J7" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+        <v>4308</v>
       </c>
     </row>
     <row r="8">
@@ -3363,40 +2986,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>蜜桃糖浆 Peach Syrup</t>
+          <t>Peach Syrup</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Peach Syrup</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
           <t>M28</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>18 months</t>
-        </is>
+      <c r="G8" t="n">
+        <v>18</v>
+      </c>
+      <c r="H8" t="n">
+        <v>16.8</v>
       </c>
       <c r="I8" t="n">
-        <v>16.8</v>
+        <v>2000</v>
       </c>
       <c r="J8" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+        <v>6786</v>
       </c>
     </row>
     <row r="9">
@@ -3412,32 +3028,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>荔枝糖浆 Lychee Syrup</t>
+          <t>Lychee Syrup</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lychee Syrup</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
           <t>M29</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="J9" t="n">
+        <v>3480</v>
       </c>
     </row>
     <row r="10">
@@ -3453,40 +3064,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>芒果糖浆 Mango Syrup</t>
+          <t>Mango Syrup</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mango Syrup</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
           <t>M30</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>18 months</t>
-        </is>
+      <c r="G10" t="n">
+        <v>18</v>
+      </c>
+      <c r="H10" t="n">
+        <v>15.6</v>
       </c>
       <c r="I10" t="n">
-        <v>15.6</v>
+        <v>2000</v>
       </c>
       <c r="J10" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+        <v>7382</v>
       </c>
     </row>
     <row r="11">
@@ -3502,11 +3106,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -3515,19 +3119,14 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Testing Material 1</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
           <t>T01</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="J11" t="n">
+        <v>390</v>
       </c>
     </row>
     <row r="12">
@@ -3543,11 +3142,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3556,18 +3155,13 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Testing Material 2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
           <t>T02</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
+      <c r="J12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3584,11 +3178,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3597,18 +3191,13 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Testing Material 3</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
           <t>T03</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
+      <c r="J13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3625,31 +3214,26 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>饮品奶油 BC01 Beverage Cream</t>
+          <t>BC01 Beverage Cream</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>BC01 Beverage Cream</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
           <t>M32</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="n">
+      <c r="J14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3666,32 +3250,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Taro Syrup 鲜芋糖浆</t>
+          <t>Taro Syrup</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Taro Syrup</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
           <t>T04</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="J15" t="n">
+        <v>7064</v>
       </c>
     </row>
     <row r="16">
@@ -3707,11 +3286,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -3720,18 +3299,13 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Watermelon Syrup</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
           <t>M31</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
+      <c r="J16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3748,11 +3322,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -3761,18 +3335,13 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange Syrup</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
           <t>M33</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
+      <c r="J17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3789,11 +3358,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -3802,18 +3371,13 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Passion Fruit Syrup</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
           <t>M34</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
+      <c r="J18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3830,32 +3394,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>全脂牛奶 Whole Milk</t>
+          <t>Whole Milk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Whole Milk</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
           <t>M35</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="J19" t="n">
+        <v>5595</v>
       </c>
     </row>
     <row r="20">
@@ -3871,31 +3430,26 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>石榴糖浆 Pomegranate Syrup</t>
+          <t>Pomegranate Syrup</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pomegranate Syrup</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
           <t>MT14</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
+      <c r="J20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3910,61 +3464,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>设备编号</t>
+          <t>Machine No.</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>门店名称</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>出料时间段</t>
+          <t>Usage Period</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>出料时间段天数</t>
+          <t>Usage Days</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>原料名称</t>
+          <t>Ingredient</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>rawMaterial_EN</t>
+          <t>Ingredient No.</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>原料代码</t>
+          <t>Shelf Life (months)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Shelf Life</t>
+          <t>Price ($)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Package_Size_Base</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Package_Size_Base</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>adjusted_usage</t>
         </is>
@@ -3983,40 +3532,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>冰糖糖浆 Fructose Syrup</t>
+          <t>Fructose Syrup</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fructose Syrup</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
           <t>M13</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>18 months</t>
-        </is>
+      <c r="G2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H2" t="n">
+        <v>15.6</v>
       </c>
       <c r="I2" t="n">
-        <v>15.6</v>
+        <v>2000</v>
       </c>
       <c r="J2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2915</v>
+        <v>2928</v>
       </c>
     </row>
     <row r="3">
@@ -4032,40 +3574,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>冰勃朗 Ice Blanc</t>
+          <t>Ice Blanc</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ice Blanc</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
           <t>M14</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>9 months</t>
-        </is>
+      <c r="G3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4357</v>
+        <v>15130</v>
       </c>
     </row>
     <row r="4">
@@ -4081,40 +3616,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>锡兰红茶茶汤 Black Tea</t>
+          <t>Black Tea</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Black Tea</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
           <t>M16</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>24 months</t>
-        </is>
+      <c r="G4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12.3</v>
       </c>
       <c r="I4" t="n">
-        <v>12.3</v>
+        <v>500</v>
       </c>
       <c r="J4" t="n">
-        <v>500</v>
-      </c>
-      <c r="K4" t="n">
-        <v>402.9</v>
+        <v>992.85</v>
       </c>
     </row>
     <row r="5">
@@ -4130,32 +3658,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>冰水 Cold Water</t>
+          <t>Cold Water</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cold Water</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
           <t>M22</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>18215</v>
+      <c r="J5" t="n">
+        <v>36585</v>
       </c>
     </row>
     <row r="6">
@@ -4171,40 +3694,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>茉莉雪芽茶汤 Green Tea</t>
+          <t>Green Tea</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Green Tea</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
           <t>M23</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>24 months</t>
-        </is>
+      <c r="G6" t="n">
+        <v>24</v>
+      </c>
+      <c r="H6" t="n">
+        <v>16.2</v>
       </c>
       <c r="I6" t="n">
-        <v>16.2</v>
+        <v>500</v>
       </c>
       <c r="J6" t="n">
-        <v>500</v>
-      </c>
-      <c r="K6" t="n">
-        <v>306</v>
+        <v>665.1</v>
       </c>
     </row>
     <row r="7">
@@ -4220,40 +3736,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>黑糖糖浆 Brown Sugar</t>
+          <t>Brown Sugar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brown Sugar</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
           <t>M27</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>18 months</t>
-        </is>
+      <c r="G7" t="n">
+        <v>18</v>
+      </c>
+      <c r="H7" t="n">
+        <v>15.6</v>
       </c>
       <c r="I7" t="n">
-        <v>15.6</v>
+        <v>2000</v>
       </c>
       <c r="J7" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4975</v>
+        <v>7295</v>
       </c>
     </row>
     <row r="8">
@@ -4269,40 +3778,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>蜜桃糖浆 Peach Syrup</t>
+          <t>Peach Syrup</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Peach Syrup</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
           <t>M28</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>18 months</t>
-        </is>
+      <c r="G8" t="n">
+        <v>18</v>
+      </c>
+      <c r="H8" t="n">
+        <v>16.8</v>
       </c>
       <c r="I8" t="n">
-        <v>16.8</v>
+        <v>2000</v>
       </c>
       <c r="J8" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2520</v>
+        <v>8450</v>
       </c>
     </row>
     <row r="9">
@@ -4318,31 +3820,26 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>荔枝糖浆 Lychee Syrup</t>
+          <t>Lychee Syrup</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lychee Syrup</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
           <t>M29</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
+      <c r="J9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4359,40 +3856,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>芒果糖浆 Mango Syrup</t>
+          <t>Mango Syrup</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mango Syrup</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
           <t>M30</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>18 months</t>
-        </is>
+      <c r="G10" t="n">
+        <v>18</v>
+      </c>
+      <c r="H10" t="n">
+        <v>15.6</v>
       </c>
       <c r="I10" t="n">
-        <v>15.6</v>
+        <v>2000</v>
       </c>
       <c r="J10" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3345</v>
+        <v>10433</v>
       </c>
     </row>
     <row r="11">
@@ -4408,11 +3898,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -4421,18 +3911,13 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Testing Material 1</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
           <t>T01</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
+      <c r="J11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4449,11 +3934,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -4462,18 +3947,13 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Testing Material 2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
           <t>T02</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
+      <c r="J12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4490,11 +3970,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -4503,18 +3983,13 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Testing Material 3</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
           <t>T03</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
+      <c r="J13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4531,31 +4006,26 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>饮品奶油 BC01 Beverage Cream</t>
+          <t>BC01 Beverage Cream</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>BC01 Beverage Cream</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
           <t>M32</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="n">
+      <c r="J14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4572,31 +4042,26 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Taro Syrup 鲜芋糖浆</t>
+          <t>Taro Syrup</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Taro Syrup</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
           <t>T04</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
+      <c r="J15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4613,11 +4078,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -4626,18 +4091,13 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Watermelon Syrup</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
           <t>M31</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
+      <c r="J16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4654,11 +4114,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -4667,18 +4127,13 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange Syrup</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
           <t>M33</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
+      <c r="J17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4695,11 +4150,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -4708,18 +4163,13 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Passion Fruit Syrup</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
           <t>M34</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
+      <c r="J18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4736,31 +4186,26 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>全脂牛奶 Whole Milk</t>
+          <t>Whole Milk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Whole Milk</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
           <t>M35</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
+      <c r="J19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4777,31 +4222,26 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>石榴糖浆 Pomegranate Syrup</t>
+          <t>Pomegranate Syrup</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pomegranate Syrup</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
           <t>MT14</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
+      <c r="J20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4816,61 +4256,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>设备编号</t>
+          <t>Machine No.</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>门店名称</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>出料时间段</t>
+          <t>Usage Period</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>出料时间段天数</t>
+          <t>Usage Days</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>原料名称</t>
+          <t>Ingredient</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>rawMaterial_EN</t>
+          <t>Ingredient No.</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>原料代码</t>
+          <t>Shelf Life (months)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Shelf Life</t>
+          <t>Price ($)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Package_Size_Base</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Package_Size_Base</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>adjusted_usage</t>
         </is>
@@ -4889,40 +4324,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>冰糖糖浆 Fructose Syrup</t>
+          <t>Fructose Syrup</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fructose Syrup</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
           <t>M13</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>18 months</t>
-        </is>
+      <c r="G2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H2" t="n">
+        <v>15.6</v>
       </c>
       <c r="I2" t="n">
-        <v>15.6</v>
+        <v>2000</v>
       </c>
       <c r="J2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+        <v>3031</v>
       </c>
     </row>
     <row r="3">
@@ -4938,40 +4366,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>冰勃朗 Ice Blanc</t>
+          <t>Ice Blanc</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ice Blanc</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
           <t>M14</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>9 months</t>
-        </is>
+      <c r="G3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+        <v>18603</v>
       </c>
     </row>
     <row r="4">
@@ -4987,40 +4408,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>锡兰红茶茶汤 Black Tea</t>
+          <t>Black Tea</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Black Tea</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
           <t>M16</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>24 months</t>
-        </is>
+      <c r="G4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12.3</v>
       </c>
       <c r="I4" t="n">
-        <v>12.3</v>
+        <v>500</v>
       </c>
       <c r="J4" t="n">
-        <v>500</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+        <v>636.9</v>
       </c>
     </row>
     <row r="5">
@@ -5036,32 +4450,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>冰水 Cold Water</t>
+          <t>Cold Water</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cold Water</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
           <t>M22</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="J5" t="n">
+        <v>34753</v>
       </c>
     </row>
     <row r="6">
@@ -5077,40 +4486,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>茉莉雪芽茶汤 Green Tea</t>
+          <t>Green Tea</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Green Tea</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
           <t>M23</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>24 months</t>
-        </is>
+      <c r="G6" t="n">
+        <v>24</v>
+      </c>
+      <c r="H6" t="n">
+        <v>16.2</v>
       </c>
       <c r="I6" t="n">
-        <v>16.2</v>
+        <v>500</v>
       </c>
       <c r="J6" t="n">
-        <v>500</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+        <v>718.26</v>
       </c>
     </row>
     <row r="7">
@@ -5126,40 +4528,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>黑糖糖浆 Brown Sugar</t>
+          <t>Brown Sugar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brown Sugar</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
           <t>M27</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>18 months</t>
-        </is>
+      <c r="G7" t="n">
+        <v>18</v>
+      </c>
+      <c r="H7" t="n">
+        <v>15.6</v>
       </c>
       <c r="I7" t="n">
-        <v>15.6</v>
+        <v>2000</v>
       </c>
       <c r="J7" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="8">
@@ -5175,40 +4570,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>蜜桃糖浆 Peach Syrup</t>
+          <t>Peach Syrup</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Peach Syrup</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
           <t>M28</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>18 months</t>
-        </is>
+      <c r="G8" t="n">
+        <v>18</v>
+      </c>
+      <c r="H8" t="n">
+        <v>16.8</v>
       </c>
       <c r="I8" t="n">
-        <v>16.8</v>
+        <v>2000</v>
       </c>
       <c r="J8" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+        <v>15945</v>
       </c>
     </row>
     <row r="9">
@@ -5224,31 +4612,26 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>荔枝糖浆 Lychee Syrup</t>
+          <t>Lychee Syrup</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lychee Syrup</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
           <t>M29</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
+      <c r="J9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5265,40 +4648,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>芒果糖浆 Mango Syrup</t>
+          <t>Mango Syrup</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mango Syrup</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
           <t>M30</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>18 months</t>
-        </is>
+      <c r="G10" t="n">
+        <v>18</v>
+      </c>
+      <c r="H10" t="n">
+        <v>15.6</v>
       </c>
       <c r="I10" t="n">
-        <v>15.6</v>
+        <v>2000</v>
       </c>
       <c r="J10" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+        <v>17867</v>
       </c>
     </row>
     <row r="11">
@@ -5314,11 +4690,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -5327,18 +4703,13 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Testing Material 1</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
           <t>T01</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
+      <c r="J11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5355,11 +4726,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -5368,18 +4739,13 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Testing Material 2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
           <t>T02</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
+      <c r="J12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5396,11 +4762,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -5409,18 +4775,13 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Testing Material 3</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
           <t>T03</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
+      <c r="J13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5437,31 +4798,26 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>饮品奶油 BC01 Beverage Cream</t>
+          <t>BC01 Beverage Cream</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>BC01 Beverage Cream</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
           <t>M32</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="n">
+      <c r="J14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5478,31 +4834,26 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Taro Syrup 鲜芋糖浆</t>
+          <t>Taro Syrup</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Taro Syrup</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
           <t>T04</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
+      <c r="J15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5519,11 +4870,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -5532,18 +4883,13 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Watermelon Syrup</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
           <t>M31</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
+      <c r="J16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5560,11 +4906,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -5573,18 +4919,13 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange Syrup</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
           <t>M33</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
+      <c r="J17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5601,11 +4942,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -5614,19 +4955,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Passion Fruit Syrup</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
           <t>M34</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="J18" t="n">
+        <v>565</v>
       </c>
     </row>
     <row r="19">
@@ -5642,31 +4978,26 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>全脂牛奶 Whole Milk</t>
+          <t>Whole Milk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Whole Milk</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
           <t>M35</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
+      <c r="J19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5683,31 +5014,26 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-01-01~2026-01-31</t>
+          <t>2026-04-01~2026-04-30</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>石榴糖浆 Pomegranate Syrup</t>
+          <t>Pomegranate Syrup</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pomegranate Syrup</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
           <t>MT14</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
+      <c r="J20" t="n">
         <v>0</v>
       </c>
     </row>
